--- a/planilhas/estoque emc lab.xlsx
+++ b/planilhas/estoque emc lab.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\LGE\operacao\Areas\CEM\André\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AF4F35-B1E3-4297-9411-D90803355F46}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08538885-DD6E-4A53-BA47-AE8B3590B5F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="18" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resistores" sheetId="1" r:id="rId1"/>
@@ -1251,48 +1251,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1302,38 +1260,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1377,33 +1311,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1411,20 +1321,110 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1727,38 +1727,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="A4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1970,23 +1970,23 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -2000,7 +2000,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="14" t="s">
         <v>141</v>
       </c>
       <c r="C7" s="3">
@@ -2009,7 +2009,7 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="14" t="s">
         <v>139</v>
       </c>
       <c r="C8" s="3">
@@ -2018,7 +2018,7 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="14" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="3">
@@ -2027,7 +2027,7 @@
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="14" t="s">
         <v>143</v>
       </c>
       <c r="C10" s="3">
@@ -2036,7 +2036,7 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C11" s="3">
@@ -2045,7 +2045,7 @@
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="14" t="s">
         <v>145</v>
       </c>
       <c r="C12" s="3">
@@ -2054,7 +2054,7 @@
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="14" t="s">
         <v>146</v>
       </c>
       <c r="C13" s="3">
@@ -2063,7 +2063,7 @@
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="14" t="s">
         <v>147</v>
       </c>
       <c r="C14" s="3">
@@ -2072,27 +2072,27 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="28"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="28"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="28"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="28"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="28"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
@@ -2128,17 +2128,17 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
@@ -2146,13 +2146,13 @@
       <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -2160,17 +2160,17 @@
       <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="22" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
@@ -2187,7 +2187,7 @@
       <c r="C6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="39"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="7" t="s">
         <v>53</v>
       </c>
@@ -2201,16 +2201,16 @@
       <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="19">
         <v>25</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="42"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="3" t="s">
         <v>82</v>
       </c>
@@ -2220,14 +2220,14 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="19">
         <v>15</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="3" t="s">
         <v>83</v>
       </c>
@@ -2237,16 +2237,16 @@
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="19">
         <v>12</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="42"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="3" t="s">
         <v>84</v>
       </c>
@@ -2259,13 +2259,13 @@
       <c r="A10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="19">
         <v>2</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="42"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="3" t="s">
         <v>86</v>
       </c>
@@ -2275,16 +2275,16 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="40">
-        <v>1</v>
-      </c>
-      <c r="C11" s="60" t="s">
+      <c r="B11" s="19">
+        <v>1</v>
+      </c>
+      <c r="C11" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="42"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="3" t="s">
         <v>87</v>
       </c>
@@ -2297,11 +2297,11 @@
       <c r="A12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="40">
-        <v>1</v>
-      </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="42"/>
+      <c r="B12" s="19">
+        <v>1</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="3" t="s">
         <v>88</v>
       </c>
@@ -2314,11 +2314,11 @@
       <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="40">
-        <v>1</v>
-      </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="42"/>
+      <c r="B13" s="19">
+        <v>1</v>
+      </c>
+      <c r="C13" s="59"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2334,8 +2334,8 @@
       <c r="B14" s="3">
         <v>2</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="42"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2351,10 +2351,10 @@
       <c r="B15" s="3">
         <v>1</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="61" t="s">
         <v>220</v>
       </c>
-      <c r="D15" s="42"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2370,8 +2370,8 @@
       <c r="B16" s="3">
         <v>1</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
@@ -2380,8 +2380,8 @@
       <c r="B17" s="3">
         <v>1</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="42"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="20"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -2390,11 +2390,11 @@
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
@@ -2403,11 +2403,11 @@
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
@@ -2416,11 +2416,11 @@
       <c r="B20" s="3">
         <v>1</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -2429,11 +2429,11 @@
       <c r="B21" s="3">
         <v>1</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
@@ -2442,11 +2442,11 @@
       <c r="B22" s="3">
         <v>1</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
@@ -2455,11 +2455,11 @@
       <c r="B23" s="3">
         <v>1</v>
       </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -2468,11 +2468,11 @@
       <c r="B24" s="3">
         <v>1</v>
       </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
@@ -2481,11 +2481,11 @@
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -2494,11 +2494,11 @@
       <c r="B26" s="3">
         <v>1</v>
       </c>
-      <c r="C26" s="66"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
@@ -2507,13 +2507,13 @@
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
@@ -2522,13 +2522,13 @@
       <c r="B28" s="3">
         <v>1</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -2537,11 +2537,11 @@
       <c r="B29" s="3">
         <v>2</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
@@ -2550,7 +2550,7 @@
       <c r="B30" s="3">
         <v>3</v>
       </c>
-      <c r="C30" s="25"/>
+      <c r="C30" s="65"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
@@ -2559,16 +2559,16 @@
       <c r="B31" s="3">
         <v>1</v>
       </c>
-      <c r="C31" s="63"/>
+      <c r="C31" s="36"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B32" s="69">
-        <v>1</v>
-      </c>
-      <c r="C32" s="67"/>
+      <c r="B32" s="39">
+        <v>1</v>
+      </c>
+      <c r="C32" s="37"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
@@ -2577,7 +2577,7 @@
       <c r="B33" s="3">
         <v>2</v>
       </c>
-      <c r="C33" s="67"/>
+      <c r="C33" s="37"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -2586,7 +2586,7 @@
       <c r="B34" s="3">
         <v>1</v>
       </c>
-      <c r="C34" s="67"/>
+      <c r="C34" s="37"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
@@ -2595,7 +2595,7 @@
       <c r="B35" s="3">
         <v>1</v>
       </c>
-      <c r="C35" s="67"/>
+      <c r="C35" s="37"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
@@ -2604,7 +2604,7 @@
       <c r="B36" s="3">
         <v>1</v>
       </c>
-      <c r="C36" s="68"/>
+      <c r="C36" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2633,25 +2633,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-    </row>
-    <row r="6" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+    </row>
+    <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>203</v>
       </c>
@@ -2805,25 +2805,25 @@
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-    </row>
-    <row r="5" spans="2:4" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+    </row>
+    <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>203</v>
       </c>
@@ -2900,23 +2900,23 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="69" t="s">
         <v>268</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
     </row>
     <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -3093,23 +3093,23 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:20" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
     </row>
     <row r="5" spans="2:20" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -3150,7 +3150,7 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="2:20" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="41" t="s">
         <v>274</v>
       </c>
       <c r="C9" s="13">
@@ -3231,25 +3231,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-    </row>
-    <row r="6" spans="2:4" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+    </row>
+    <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>203</v>
       </c>
@@ -3327,23 +3327,23 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="2:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -3610,8 +3610,8 @@
         <v>2</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
@@ -3621,8 +3621,8 @@
         <v>1</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
@@ -3708,23 +3708,23 @@
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -3887,25 +3887,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-    </row>
-    <row r="6" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+    </row>
+    <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>53</v>
       </c>
@@ -4078,25 +4078,25 @@
   <sheetData>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
     </row>
     <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>53</v>
       </c>
@@ -4108,7 +4108,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="14" t="s">
         <v>148</v>
       </c>
       <c r="C8" s="3">
@@ -4117,7 +4117,7 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="14" t="s">
         <v>154</v>
       </c>
       <c r="C9" s="3">
@@ -4126,7 +4126,7 @@
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="14" t="s">
         <v>149</v>
       </c>
       <c r="C10" s="3">
@@ -4135,7 +4135,7 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>150</v>
       </c>
       <c r="C11" s="3">
@@ -4144,7 +4144,7 @@
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="14" t="s">
         <v>151</v>
       </c>
       <c r="C12" s="3">
@@ -4153,7 +4153,7 @@
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="14" t="s">
         <v>152</v>
       </c>
       <c r="C13" s="3">
@@ -4162,7 +4162,7 @@
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="14" t="s">
         <v>153</v>
       </c>
       <c r="C14" s="3">
@@ -4171,32 +4171,32 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="28"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="28"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="28"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="28"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="28"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="28"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
@@ -4221,178 +4221,178 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="33">
         <v>2</v>
       </c>
-      <c r="D7" s="55"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="33">
         <v>5</v>
       </c>
-      <c r="D8" s="55"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="55">
-        <v>1</v>
-      </c>
-      <c r="D9" s="55"/>
+      <c r="C9" s="33">
+        <v>1</v>
+      </c>
+      <c r="D9" s="33"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="55">
-        <v>1</v>
-      </c>
-      <c r="D10" s="55"/>
+      <c r="C10" s="33">
+        <v>1</v>
+      </c>
+      <c r="D10" s="33"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="33">
         <v>2</v>
       </c>
-      <c r="D11" s="55"/>
+      <c r="D11" s="33"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="33">
         <v>5</v>
       </c>
-      <c r="D12" s="55"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="33">
         <v>3</v>
       </c>
-      <c r="D13" s="55"/>
+      <c r="D13" s="33"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="55">
-        <v>1</v>
-      </c>
-      <c r="D14" s="55"/>
+      <c r="C14" s="33">
+        <v>1</v>
+      </c>
+      <c r="D14" s="33"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="55">
-        <v>1</v>
-      </c>
-      <c r="D15" s="55"/>
+      <c r="C15" s="33">
+        <v>1</v>
+      </c>
+      <c r="D15" s="33"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="55">
-        <v>1</v>
-      </c>
-      <c r="D16" s="55"/>
+      <c r="C16" s="33">
+        <v>1</v>
+      </c>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="33">
         <v>6</v>
       </c>
-      <c r="D17" s="55"/>
+      <c r="D17" s="33"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="33">
         <v>9</v>
       </c>
-      <c r="D18" s="55"/>
+      <c r="D18" s="33"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="33">
         <v>10</v>
       </c>
-      <c r="D19" s="55"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="48">
+      <c r="C20" s="26">
         <v>2</v>
       </c>
-      <c r="D20" s="49"/>
+      <c r="D20" s="27"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="26">
         <v>5</v>
       </c>
-      <c r="D21" s="49"/>
+      <c r="D21" s="27"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="C22" s="48">
-        <v>1</v>
-      </c>
-      <c r="D22" s="49"/>
+      <c r="C22" s="26">
+        <v>1</v>
+      </c>
+      <c r="D22" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4416,25 +4416,25 @@
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>53</v>
       </c>
@@ -4502,23 +4502,23 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -4588,23 +4588,23 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
     </row>
     <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -4663,13 +4663,13 @@
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="47">
-        <v>1</v>
-      </c>
-      <c r="D12" s="46"/>
+      <c r="C12" s="25">
+        <v>1</v>
+      </c>
+      <c r="D12" s="24"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -4681,7 +4681,7 @@
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="40" t="s">
         <v>233</v>
       </c>
       <c r="C14" s="13">
@@ -4710,25 +4710,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="50" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-    </row>
-    <row r="6" spans="2:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+    </row>
+    <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>53</v>
       </c>
@@ -4785,16 +4785,16 @@
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="24"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="50"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4817,23 +4817,23 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
     </row>
     <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -4892,14 +4892,14 @@
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="46"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="24"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="50"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4922,23 +4922,23 @@
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="2:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -4952,7 +4952,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="14" t="s">
         <v>124</v>
       </c>
       <c r="C7" s="3">
@@ -4961,7 +4961,7 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="14" t="s">
         <v>135</v>
       </c>
       <c r="C8" s="3">
@@ -4970,7 +4970,7 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="14" t="s">
         <v>134</v>
       </c>
       <c r="C9" s="3">
@@ -4979,7 +4979,7 @@
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="14" t="s">
         <v>125</v>
       </c>
       <c r="C10" s="3">
@@ -4988,7 +4988,7 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="3">
@@ -4997,7 +4997,7 @@
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="14" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="3">
@@ -5006,7 +5006,7 @@
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="14" t="s">
         <v>132</v>
       </c>
       <c r="C13" s="3">
@@ -5015,7 +5015,7 @@
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="14" t="s">
         <v>131</v>
       </c>
       <c r="C14" s="3">
@@ -5024,7 +5024,7 @@
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="14" t="s">
         <v>137</v>
       </c>
       <c r="C15" s="3">
@@ -5033,7 +5033,7 @@
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="14" t="s">
         <v>127</v>
       </c>
       <c r="C16" s="3">
@@ -5042,7 +5042,7 @@
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="14" t="s">
         <v>128</v>
       </c>
       <c r="C17" s="3">
@@ -5051,7 +5051,7 @@
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="14" t="s">
         <v>129</v>
       </c>
       <c r="C18" s="3">
@@ -5060,7 +5060,7 @@
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="14" t="s">
         <v>136</v>
       </c>
       <c r="C19" s="3">
